--- a/artfynd/A 9157-2023 artfynd.xlsx
+++ b/artfynd/A 9157-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9157-2023 artfynd.xlsx
+++ b/artfynd/A 9157-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66548123</v>
+        <v>66548119</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Matsdal Klitvallsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544162.2774522186</v>
+        <v>544126</v>
       </c>
       <c r="R2" t="n">
-        <v>7237687.892086631</v>
+        <v>7237762</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -752,21 +743,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -778,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>26544</t>
+          <t>26541</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -799,16 +780,11 @@
         <v>66548115</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -840,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544209.5548490728</v>
+        <v>544210</v>
       </c>
       <c r="R3" t="n">
-        <v>7237836.528153325</v>
+        <v>7237837</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -873,19 +849,9 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,16 +886,11 @@
         <v>66548117</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -961,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544126.3507823227</v>
+        <v>544126</v>
       </c>
       <c r="R4" t="n">
-        <v>7237761.52755963</v>
+        <v>7237762</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -994,19 +955,9 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,50 +989,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66548124</v>
+        <v>66548123</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Matsdal Klitvallsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544162.2774522186</v>
+        <v>544162</v>
       </c>
       <c r="R5" t="n">
-        <v>7237687.892086631</v>
+        <v>7237688</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1111,21 +1061,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1137,7 +1077,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>26545</t>
+          <t>26544</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1155,15 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66548119</v>
+        <v>67152605</v>
       </c>
       <c r="B6" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,37 +1106,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Matsdal Klitvallsliden, Ås lm</t>
+          <t>Klintvallsliden, Dikanäs, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544126.3507823227</v>
+        <v>542844</v>
       </c>
       <c r="R6" t="n">
-        <v>7237761.52755963</v>
+        <v>7238740</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,22 +1160,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,24 +1176,320 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>26541</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>67152590</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Klintvallsliden, Dikanäs, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>542854</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7238734</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-08-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-08-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>66548116</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Matsdal Klitvallsliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>544210</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7237837</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2014-09-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2014-09-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>26539</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Malin Sahlin</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Via Malin Sahlin</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>67152618</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Klintvallsliden, Dikanäs, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>543066</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7238897</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-08-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-08-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
